--- a/wet_lab_analysis/NMR/B1_quant.xlsx
+++ b/wet_lab_analysis/NMR/B1_quant.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d2b4f9dfd505079b/Dokumente/Uni/Master/Amsterdam/Master_Thesis/git/wet_lab_analysis/NMR/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="302" documentId="8_{C988D63D-C2FF-443C-874B-13642215BD54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A5BFDC7-06A1-407B-A343-3A97E8A03376}"/>
+  <xr:revisionPtr revIDLastSave="303" documentId="8_{C988D63D-C2FF-443C-874B-13642215BD54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81CA821A-1149-42AE-823A-5ED215DC63CE}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="10170" xr2:uid="{23C98EA3-8FB7-472F-A984-341AC56E66B7}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{23C98EA3-8FB7-472F-A984-341AC56E66B7}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -2085,7 +2085,7 @@
         <v>7.52</v>
       </c>
       <c r="F65">
-        <f t="shared" si="0"/>
+        <f>(D65/B65)*(9/(3/4))*1</f>
         <v>5.76</v>
       </c>
       <c r="G65">
